--- a/input/reg_health.xlsx
+++ b/input/reg_health.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="190">
   <si>
     <t>Description:</t>
   </si>
@@ -593,7 +593,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="450">
+  <fonts count="899">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -2400,6 +2400,1816 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2410,7 +4220,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="443">
+  <borders count="885">
     <border>
       <left/>
       <right/>
@@ -5512,11 +7322,3105 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="443">
+  <cellXfs count="885">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -7283,6 +12187,1774 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="449" fillId="0" borderId="442" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="451" fillId="0" borderId="443" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="453" fillId="0" borderId="444" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="455" fillId="0" borderId="445" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="457" fillId="0" borderId="446" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="459" fillId="0" borderId="447" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="460" fillId="0" borderId="448" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="461" fillId="0" borderId="449" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="462" fillId="0" borderId="450" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="463" fillId="0" borderId="451" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="464" fillId="0" borderId="452" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="465" fillId="0" borderId="453" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="466" fillId="0" borderId="454" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="467" fillId="0" borderId="455" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="468" fillId="0" borderId="456" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="469" fillId="0" borderId="457" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="470" fillId="0" borderId="458" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="471" fillId="0" borderId="459" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="472" fillId="0" borderId="460" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="473" fillId="0" borderId="461" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="474" fillId="0" borderId="462" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="475" fillId="0" borderId="463" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="476" fillId="0" borderId="464" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="477" fillId="0" borderId="465" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="478" fillId="0" borderId="466" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="479" fillId="0" borderId="467" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="480" fillId="0" borderId="468" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="481" fillId="0" borderId="469" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="482" fillId="0" borderId="470" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="483" fillId="0" borderId="471" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="484" fillId="0" borderId="472" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="485" fillId="0" borderId="473" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="486" fillId="0" borderId="474" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="487" fillId="0" borderId="475" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="488" fillId="0" borderId="476" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="489" fillId="0" borderId="477" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="490" fillId="0" borderId="478" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="491" fillId="0" borderId="479" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="492" fillId="0" borderId="480" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="493" fillId="0" borderId="481" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="494" fillId="0" borderId="482" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="495" fillId="0" borderId="483" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="496" fillId="0" borderId="484" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="497" fillId="0" borderId="485" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="498" fillId="0" borderId="486" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="499" fillId="0" borderId="487" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="500" fillId="0" borderId="488" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="501" fillId="0" borderId="489" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="502" fillId="0" borderId="490" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="503" fillId="0" borderId="491" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="504" fillId="0" borderId="492" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="505" fillId="0" borderId="493" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="506" fillId="0" borderId="494" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="507" fillId="0" borderId="495" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="508" fillId="0" borderId="496" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="509" fillId="0" borderId="497" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="510" fillId="0" borderId="498" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="511" fillId="0" borderId="499" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="512" fillId="0" borderId="500" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="513" fillId="0" borderId="501" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="514" fillId="0" borderId="502" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="515" fillId="0" borderId="503" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="516" fillId="0" borderId="504" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="517" fillId="0" borderId="505" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="518" fillId="0" borderId="506" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="519" fillId="0" borderId="507" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="520" fillId="0" borderId="508" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="521" fillId="0" borderId="509" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="522" fillId="0" borderId="510" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="523" fillId="0" borderId="511" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="524" fillId="0" borderId="512" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="525" fillId="0" borderId="513" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="526" fillId="0" borderId="514" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="527" fillId="0" borderId="515" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="528" fillId="0" borderId="516" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="529" fillId="0" borderId="517" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="530" fillId="0" borderId="518" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="531" fillId="0" borderId="519" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="532" fillId="0" borderId="520" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="533" fillId="0" borderId="521" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="534" fillId="0" borderId="522" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="535" fillId="0" borderId="523" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="536" fillId="0" borderId="524" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="537" fillId="0" borderId="525" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="538" fillId="0" borderId="526" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="539" fillId="0" borderId="527" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="540" fillId="0" borderId="528" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="541" fillId="0" borderId="529" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="542" fillId="0" borderId="530" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="543" fillId="0" borderId="531" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="544" fillId="0" borderId="532" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="545" fillId="0" borderId="533" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="546" fillId="0" borderId="534" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="547" fillId="0" borderId="535" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="548" fillId="0" borderId="536" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="549" fillId="0" borderId="537" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="550" fillId="0" borderId="538" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="551" fillId="0" borderId="539" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="552" fillId="0" borderId="540" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="553" fillId="0" borderId="541" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="554" fillId="0" borderId="542" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="555" fillId="0" borderId="543" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="556" fillId="0" borderId="544" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="557" fillId="0" borderId="545" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="558" fillId="0" borderId="546" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="559" fillId="0" borderId="547" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="560" fillId="0" borderId="548" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="561" fillId="0" borderId="549" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="562" fillId="0" borderId="550" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="563" fillId="0" borderId="551" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="564" fillId="0" borderId="552" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="565" fillId="0" borderId="553" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="566" fillId="0" borderId="554" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="567" fillId="0" borderId="555" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="568" fillId="0" borderId="556" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="569" fillId="0" borderId="557" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="570" fillId="0" borderId="558" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="571" fillId="0" borderId="559" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="572" fillId="0" borderId="560" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="573" fillId="0" borderId="561" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="574" fillId="0" borderId="562" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="575" fillId="0" borderId="563" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="576" fillId="0" borderId="564" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="577" fillId="0" borderId="565" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="578" fillId="0" borderId="566" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="579" fillId="0" borderId="567" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="580" fillId="0" borderId="568" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="581" fillId="0" borderId="569" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="582" fillId="0" borderId="570" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="583" fillId="0" borderId="571" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="584" fillId="0" borderId="572" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="585" fillId="0" borderId="573" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="586" fillId="0" borderId="574" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="587" fillId="0" borderId="575" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="588" fillId="0" borderId="576" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="589" fillId="0" borderId="577" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="590" fillId="0" borderId="578" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="591" fillId="0" borderId="579" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="592" fillId="0" borderId="580" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="593" fillId="0" borderId="581" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="594" fillId="0" borderId="582" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="595" fillId="0" borderId="583" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="596" fillId="0" borderId="584" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="597" fillId="0" borderId="585" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="598" fillId="0" borderId="586" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="599" fillId="0" borderId="587" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="600" fillId="0" borderId="588" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="601" fillId="0" borderId="589" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="602" fillId="0" borderId="590" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="603" fillId="0" borderId="591" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="604" fillId="0" borderId="592" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="605" fillId="0" borderId="593" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="606" fillId="0" borderId="594" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="607" fillId="0" borderId="595" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="608" fillId="0" borderId="596" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="609" fillId="0" borderId="597" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="610" fillId="0" borderId="598" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="611" fillId="0" borderId="599" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="612" fillId="0" borderId="600" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="613" fillId="0" borderId="601" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="614" fillId="0" borderId="602" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="615" fillId="0" borderId="603" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="616" fillId="0" borderId="604" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="617" fillId="0" borderId="605" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="618" fillId="0" borderId="606" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="619" fillId="0" borderId="607" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="620" fillId="0" borderId="608" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="621" fillId="0" borderId="609" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="622" fillId="0" borderId="610" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="623" fillId="0" borderId="611" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="624" fillId="0" borderId="612" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="625" fillId="0" borderId="613" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="626" fillId="0" borderId="614" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="627" fillId="0" borderId="615" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="628" fillId="0" borderId="616" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="629" fillId="0" borderId="617" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="630" fillId="0" borderId="618" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="631" fillId="0" borderId="619" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="632" fillId="0" borderId="620" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="633" fillId="0" borderId="621" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="634" fillId="0" borderId="622" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="635" fillId="0" borderId="623" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="636" fillId="0" borderId="624" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="637" fillId="0" borderId="625" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="638" fillId="0" borderId="626" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="639" fillId="0" borderId="627" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="640" fillId="0" borderId="628" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="641" fillId="0" borderId="629" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="642" fillId="0" borderId="630" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="643" fillId="0" borderId="631" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="644" fillId="0" borderId="632" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="645" fillId="0" borderId="633" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="646" fillId="0" borderId="634" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="647" fillId="0" borderId="635" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="648" fillId="0" borderId="636" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="649" fillId="0" borderId="637" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="650" fillId="0" borderId="638" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="651" fillId="0" borderId="639" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="652" fillId="0" borderId="640" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="653" fillId="0" borderId="641" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="654" fillId="0" borderId="642" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="655" fillId="0" borderId="643" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="656" fillId="0" borderId="644" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="657" fillId="0" borderId="645" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="658" fillId="0" borderId="646" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="659" fillId="0" borderId="647" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="660" fillId="0" borderId="648" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="661" fillId="0" borderId="649" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="662" fillId="0" borderId="650" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="663" fillId="0" borderId="651" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="664" fillId="0" borderId="652" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="665" fillId="0" borderId="653" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="666" fillId="0" borderId="654" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="667" fillId="0" borderId="655" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="668" fillId="0" borderId="656" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="669" fillId="0" borderId="657" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="670" fillId="0" borderId="658" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="671" fillId="0" borderId="659" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="672" fillId="0" borderId="660" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="673" fillId="0" borderId="661" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="674" fillId="0" borderId="662" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="675" fillId="0" borderId="663" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="676" fillId="0" borderId="664" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="677" fillId="0" borderId="665" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="678" fillId="0" borderId="666" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="679" fillId="0" borderId="667" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="680" fillId="0" borderId="668" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="681" fillId="0" borderId="669" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="682" fillId="0" borderId="670" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="683" fillId="0" borderId="671" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="684" fillId="0" borderId="672" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="685" fillId="0" borderId="673" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="686" fillId="0" borderId="674" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="687" fillId="0" borderId="675" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="688" fillId="0" borderId="676" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="689" fillId="0" borderId="677" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="690" fillId="0" borderId="678" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="691" fillId="0" borderId="679" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="692" fillId="0" borderId="680" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="693" fillId="0" borderId="681" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="694" fillId="0" borderId="682" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="695" fillId="0" borderId="683" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="696" fillId="0" borderId="684" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="697" fillId="0" borderId="685" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="698" fillId="0" borderId="686" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="699" fillId="0" borderId="687" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="700" fillId="0" borderId="688" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="701" fillId="0" borderId="689" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="702" fillId="0" borderId="690" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="703" fillId="0" borderId="691" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="704" fillId="0" borderId="692" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="705" fillId="0" borderId="693" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="706" fillId="0" borderId="694" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="707" fillId="0" borderId="695" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="708" fillId="0" borderId="696" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="709" fillId="0" borderId="697" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="710" fillId="0" borderId="698" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="711" fillId="0" borderId="699" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="712" fillId="0" borderId="700" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="713" fillId="0" borderId="701" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="714" fillId="0" borderId="702" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="715" fillId="0" borderId="703" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="716" fillId="0" borderId="704" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="717" fillId="0" borderId="705" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="718" fillId="0" borderId="706" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="719" fillId="0" borderId="707" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="720" fillId="0" borderId="708" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="721" fillId="0" borderId="709" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="722" fillId="0" borderId="710" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="723" fillId="0" borderId="711" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="724" fillId="0" borderId="712" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="725" fillId="0" borderId="713" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="726" fillId="0" borderId="714" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="727" fillId="0" borderId="715" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="728" fillId="0" borderId="716" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="729" fillId="0" borderId="717" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="730" fillId="0" borderId="718" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="731" fillId="0" borderId="719" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="732" fillId="0" borderId="720" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="733" fillId="0" borderId="721" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="734" fillId="0" borderId="722" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="735" fillId="0" borderId="723" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="736" fillId="0" borderId="724" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="737" fillId="0" borderId="725" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="738" fillId="0" borderId="726" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="739" fillId="0" borderId="727" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="740" fillId="0" borderId="728" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="741" fillId="0" borderId="729" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="742" fillId="0" borderId="730" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="743" fillId="0" borderId="731" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="744" fillId="0" borderId="732" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="745" fillId="0" borderId="733" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="746" fillId="0" borderId="734" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="747" fillId="0" borderId="735" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="748" fillId="0" borderId="736" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="749" fillId="0" borderId="737" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="750" fillId="0" borderId="738" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="751" fillId="0" borderId="739" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="752" fillId="0" borderId="740" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="753" fillId="0" borderId="741" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="754" fillId="0" borderId="742" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="755" fillId="0" borderId="743" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="756" fillId="0" borderId="744" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="757" fillId="0" borderId="745" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="758" fillId="0" borderId="746" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="759" fillId="0" borderId="747" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="760" fillId="0" borderId="748" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="761" fillId="0" borderId="749" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="762" fillId="0" borderId="750" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="763" fillId="0" borderId="751" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="764" fillId="0" borderId="752" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="765" fillId="0" borderId="753" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="766" fillId="0" borderId="754" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="767" fillId="0" borderId="755" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="768" fillId="0" borderId="756" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="769" fillId="0" borderId="757" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="770" fillId="0" borderId="758" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="771" fillId="0" borderId="759" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="772" fillId="0" borderId="760" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="773" fillId="0" borderId="761" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="774" fillId="0" borderId="762" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="775" fillId="0" borderId="763" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="776" fillId="0" borderId="764" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="777" fillId="0" borderId="765" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="778" fillId="0" borderId="766" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="779" fillId="0" borderId="767" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="780" fillId="0" borderId="768" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="781" fillId="0" borderId="769" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="782" fillId="0" borderId="770" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="783" fillId="0" borderId="771" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="784" fillId="0" borderId="772" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="785" fillId="0" borderId="773" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="786" fillId="0" borderId="774" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="787" fillId="0" borderId="775" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="788" fillId="0" borderId="776" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="789" fillId="0" borderId="777" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="790" fillId="0" borderId="778" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="791" fillId="0" borderId="779" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="792" fillId="0" borderId="780" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="793" fillId="0" borderId="781" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="794" fillId="0" borderId="782" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="795" fillId="0" borderId="783" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="796" fillId="0" borderId="784" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="797" fillId="0" borderId="785" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="798" fillId="0" borderId="786" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="799" fillId="0" borderId="787" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="800" fillId="0" borderId="788" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="801" fillId="0" borderId="789" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="802" fillId="0" borderId="790" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="803" fillId="0" borderId="791" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="804" fillId="0" borderId="792" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="805" fillId="0" borderId="793" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="806" fillId="0" borderId="794" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="807" fillId="0" borderId="795" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="808" fillId="0" borderId="796" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="809" fillId="0" borderId="797" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="810" fillId="0" borderId="798" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="811" fillId="0" borderId="799" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="812" fillId="0" borderId="800" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="813" fillId="0" borderId="801" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="814" fillId="0" borderId="802" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="815" fillId="0" borderId="803" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="816" fillId="0" borderId="804" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="817" fillId="0" borderId="805" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="818" fillId="0" borderId="806" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="819" fillId="0" borderId="807" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="820" fillId="0" borderId="808" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="821" fillId="0" borderId="809" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="822" fillId="0" borderId="810" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="823" fillId="0" borderId="811" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="824" fillId="0" borderId="812" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="825" fillId="0" borderId="813" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="826" fillId="0" borderId="814" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="827" fillId="0" borderId="815" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="828" fillId="0" borderId="816" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="829" fillId="0" borderId="817" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="830" fillId="0" borderId="818" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="831" fillId="0" borderId="819" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="832" fillId="0" borderId="820" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="833" fillId="0" borderId="821" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="834" fillId="0" borderId="822" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="835" fillId="0" borderId="823" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="836" fillId="0" borderId="824" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="837" fillId="0" borderId="825" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="838" fillId="0" borderId="826" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="839" fillId="0" borderId="827" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="840" fillId="0" borderId="828" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="841" fillId="0" borderId="829" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="842" fillId="0" borderId="830" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="843" fillId="0" borderId="831" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="844" fillId="0" borderId="832" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="845" fillId="0" borderId="833" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="846" fillId="0" borderId="834" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="847" fillId="0" borderId="835" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="848" fillId="0" borderId="836" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="849" fillId="0" borderId="837" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="850" fillId="0" borderId="838" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="851" fillId="0" borderId="839" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="852" fillId="0" borderId="840" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="853" fillId="0" borderId="841" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="854" fillId="0" borderId="842" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="855" fillId="0" borderId="843" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="856" fillId="0" borderId="844" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="857" fillId="0" borderId="845" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="858" fillId="0" borderId="846" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="859" fillId="0" borderId="847" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="860" fillId="0" borderId="848" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="861" fillId="0" borderId="849" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="862" fillId="0" borderId="850" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="863" fillId="0" borderId="851" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="864" fillId="0" borderId="852" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="865" fillId="0" borderId="853" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="866" fillId="0" borderId="854" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="867" fillId="0" borderId="855" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="868" fillId="0" borderId="856" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="869" fillId="0" borderId="857" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="870" fillId="0" borderId="858" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="871" fillId="0" borderId="859" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="872" fillId="0" borderId="860" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="873" fillId="0" borderId="861" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="874" fillId="0" borderId="862" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="875" fillId="0" borderId="863" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="876" fillId="0" borderId="864" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="877" fillId="0" borderId="865" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="878" fillId="0" borderId="866" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="879" fillId="0" borderId="867" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="880" fillId="0" borderId="868" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="881" fillId="0" borderId="869" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="882" fillId="0" borderId="870" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="883" fillId="0" borderId="871" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="884" fillId="0" borderId="872" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="885" fillId="0" borderId="873" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="886" fillId="0" borderId="874" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="887" fillId="0" borderId="875" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="888" fillId="0" borderId="876" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="889" fillId="0" borderId="877" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="890" fillId="0" borderId="878" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="891" fillId="0" borderId="879" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="892" fillId="0" borderId="880" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="893" fillId="0" borderId="881" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="2" fontId="894" fillId="0" borderId="882" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="896" fillId="0" borderId="883" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="898" fillId="0" borderId="884" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7299,7 +13971,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="443" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -7320,10 +13992,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="444" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="445" t="s">
         <v>0</v>
       </c>
     </row>
@@ -7362,7 +14034,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="446" t="s">
         <v>14</v>
       </c>
       <c r="B15" t="s">
@@ -7389,12 +14061,12 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="447" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="441" t="s">
+      <c r="A3" s="883" t="s">
         <v>183</v>
       </c>
     </row>
@@ -7427,7 +14099,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="442" t="s">
+      <c r="A7" s="884" t="s">
         <v>189</v>
       </c>
     </row>
@@ -7469,1597 +14141,1597 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="448" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="449" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="450" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="451" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="452" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="453">
         <v>0.072841292225491502</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="454" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="455" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="456">
         <v>-0.34580773440029722</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="457" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="458" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="459">
         <v>-0.015830927424489275</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="460" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="461" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="462">
         <v>0.00016030201916745489</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="463" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="464" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="23">
+      <c r="C6" s="465">
         <v>0.12325572195195308</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="466" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="467" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="468">
         <v>0.068845051562574089</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="469" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="470" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="471">
         <v>-0.10917815320931192</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="472" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="473" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="474">
         <v>-0.24914530231918916</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="475" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="476" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="477">
         <v>-0.38112637912921482</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="s">
+      <c r="A11" s="478" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="37" t="s">
+      <c r="B11" s="479" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="38">
+      <c r="C11" s="480">
         <v>-0.2362497795904141</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="39" t="s">
+      <c r="A12" s="481" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="40" t="s">
+      <c r="B12" s="482" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="41">
+      <c r="C12" s="483">
         <v>0.20150639795598713</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="42" t="s">
+      <c r="A13" s="484" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="43" t="s">
+      <c r="B13" s="485" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="44">
+      <c r="C13" s="486">
         <v>0.33579277501121318</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="487" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="46" t="s">
+      <c r="B14" s="488" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="47">
+      <c r="C14" s="489">
         <v>0.46010091657374708</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="48" t="s">
+      <c r="A15" s="490" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="49" t="s">
+      <c r="B15" s="491" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="50">
+      <c r="C15" s="492">
         <v>0.62881792741310283</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="51" t="s">
+      <c r="A16" s="493" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="52" t="s">
+      <c r="B16" s="494" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="53">
+      <c r="C16" s="495">
         <v>0.12392183299638665</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="54" t="s">
+      <c r="A17" s="496" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="55" t="s">
+      <c r="B17" s="497" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="56">
+      <c r="C17" s="498">
         <v>-0.08421482280431522</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="57" t="s">
+      <c r="A18" s="499" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="58" t="s">
+      <c r="B18" s="500" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="59">
+      <c r="C18" s="501">
         <v>-0.006610406828957003</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="60" t="s">
+      <c r="A19" s="502" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="61" t="s">
+      <c r="B19" s="503" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="62">
+      <c r="C19" s="504">
         <v>-0.50169489253278599</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="63" t="s">
+      <c r="A20" s="505" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="64" t="s">
+      <c r="B20" s="506" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="65">
+      <c r="C20" s="507">
         <v>-0.06887088384226478</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="66" t="s">
+      <c r="A21" s="508" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="67" t="s">
+      <c r="B21" s="509" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="68">
+      <c r="C21" s="510">
         <v>-0.0017457466573951768</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="69" t="s">
+      <c r="A22" s="511" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="70" t="s">
+      <c r="B22" s="512" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="71">
+      <c r="C22" s="513">
         <v>-0.012814671804200792</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="72" t="s">
+      <c r="A23" s="514" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="73" t="s">
+      <c r="B23" s="515" t="s">
         <v>44</v>
       </c>
-      <c r="C23" s="74">
+      <c r="C23" s="516">
         <v>0.088241304322095981</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="75" t="s">
+      <c r="A24" s="517" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="76" t="s">
+      <c r="B24" s="518" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="77">
+      <c r="C24" s="519">
         <v>0.1310653618307705</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="78" t="s">
+      <c r="A25" s="520" t="s">
         <v>19</v>
       </c>
-      <c r="B25" s="79" t="s">
+      <c r="B25" s="521" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="80">
+      <c r="C25" s="522">
         <v>0.070138316711195761</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="81" t="s">
+      <c r="A26" s="523" t="s">
         <v>19</v>
       </c>
-      <c r="B26" s="82" t="s">
+      <c r="B26" s="524" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="83">
+      <c r="C26" s="525">
         <v>0.15779437654524978</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="84" t="s">
+      <c r="A27" s="526" t="s">
         <v>19</v>
       </c>
-      <c r="B27" s="85" t="s">
+      <c r="B27" s="527" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="86">
+      <c r="C27" s="528">
         <v>0.081513797811845756</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="87" t="s">
+      <c r="A28" s="529" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="88" t="s">
+      <c r="B28" s="530" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="89">
+      <c r="C28" s="531">
         <v>0.06723521966158244</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="90" t="s">
+      <c r="A29" s="532" t="s">
         <v>19</v>
       </c>
-      <c r="B29" s="91" t="s">
+      <c r="B29" s="533" t="s">
         <v>50</v>
       </c>
-      <c r="C29" s="92">
+      <c r="C29" s="534">
         <v>0.11897652034069717</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="93" t="s">
+      <c r="A30" s="535" t="s">
         <v>19</v>
       </c>
-      <c r="B30" s="94" t="s">
+      <c r="B30" s="536" t="s">
         <v>51</v>
       </c>
-      <c r="C30" s="95">
+      <c r="C30" s="537">
         <v>0.15315956846033535</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="96" t="s">
+      <c r="A31" s="538" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="97" t="s">
+      <c r="B31" s="539" t="s">
         <v>52</v>
       </c>
-      <c r="C31" s="98">
+      <c r="C31" s="540">
         <v>0.0002877320173142045</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="99" t="s">
+      <c r="A32" s="541" t="s">
         <v>19</v>
       </c>
-      <c r="B32" s="100" t="s">
+      <c r="B32" s="542" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="101">
+      <c r="C32" s="543">
         <v>0.018201003901143362</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="102" t="s">
+      <c r="A33" s="544" t="s">
         <v>19</v>
       </c>
-      <c r="B33" s="103" t="s">
+      <c r="B33" s="545" t="s">
         <v>54</v>
       </c>
-      <c r="C33" s="104">
+      <c r="C33" s="546">
         <v>0.0068135544406481841</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="105" t="s">
+      <c r="A34" s="547" t="s">
         <v>19</v>
       </c>
-      <c r="B34" s="106" t="s">
+      <c r="B34" s="548" t="s">
         <v>55</v>
       </c>
-      <c r="C34" s="107">
+      <c r="C34" s="549">
         <v>-0.0054423284134936939</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="108" t="s">
+      <c r="A35" s="550" t="s">
         <v>19</v>
       </c>
-      <c r="B35" s="109" t="s">
+      <c r="B35" s="551" t="s">
         <v>56</v>
       </c>
-      <c r="C35" s="110">
+      <c r="C35" s="552">
         <v>-0.0094373723332431131</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="111" t="s">
+      <c r="A36" s="553" t="s">
         <v>19</v>
       </c>
-      <c r="B36" s="112" t="s">
+      <c r="B36" s="554" t="s">
         <v>57</v>
       </c>
-      <c r="C36" s="113">
+      <c r="C36" s="555">
         <v>-0.00036661670728757589</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="114" t="s">
+      <c r="A37" s="556" t="s">
         <v>19</v>
       </c>
-      <c r="B37" s="115" t="s">
+      <c r="B37" s="557" t="s">
         <v>58</v>
       </c>
-      <c r="C37" s="116">
+      <c r="C37" s="558">
         <v>-5.0385157377847154</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="117" t="s">
+      <c r="A38" s="559" t="s">
         <v>20</v>
       </c>
-      <c r="B38" s="118" t="s">
+      <c r="B38" s="560" t="s">
         <v>23</v>
       </c>
-      <c r="C38" s="119">
+      <c r="C38" s="561">
         <v>-0.27367834925302903</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="120" t="s">
+      <c r="A39" s="562" t="s">
         <v>20</v>
       </c>
-      <c r="B39" s="121" t="s">
+      <c r="B39" s="563" t="s">
         <v>24</v>
       </c>
-      <c r="C39" s="122">
+      <c r="C39" s="564">
         <v>-0.33199044682795087</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="123" t="s">
+      <c r="A40" s="565" t="s">
         <v>20</v>
       </c>
-      <c r="B40" s="124" t="s">
+      <c r="B40" s="566" t="s">
         <v>25</v>
       </c>
-      <c r="C40" s="125">
+      <c r="C40" s="567">
         <v>-0.045342655402369286</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="126" t="s">
+      <c r="A41" s="568" t="s">
         <v>20</v>
       </c>
-      <c r="B41" s="127" t="s">
+      <c r="B41" s="569" t="s">
         <v>26</v>
       </c>
-      <c r="C41" s="128">
+      <c r="C41" s="570">
         <v>0.00034904995000598071</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="129" t="s">
+      <c r="A42" s="571" t="s">
         <v>20</v>
       </c>
-      <c r="B42" s="130" t="s">
+      <c r="B42" s="572" t="s">
         <v>27</v>
       </c>
-      <c r="C42" s="131">
+      <c r="C42" s="573">
         <v>0.12993223955843955</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="132" t="s">
+      <c r="A43" s="574" t="s">
         <v>20</v>
       </c>
-      <c r="B43" s="133" t="s">
+      <c r="B43" s="575" t="s">
         <v>28</v>
       </c>
-      <c r="C43" s="134">
+      <c r="C43" s="576">
         <v>0.075818075589050821</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="135" t="s">
+      <c r="A44" s="577" t="s">
         <v>20</v>
       </c>
-      <c r="B44" s="136" t="s">
+      <c r="B44" s="578" t="s">
         <v>29</v>
       </c>
-      <c r="C44" s="137">
+      <c r="C44" s="579">
         <v>-0.17392426100891045</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="138" t="s">
+      <c r="A45" s="580" t="s">
         <v>20</v>
       </c>
-      <c r="B45" s="139" t="s">
+      <c r="B45" s="581" t="s">
         <v>30</v>
       </c>
-      <c r="C45" s="140">
+      <c r="C45" s="582">
         <v>-0.37073600431857345</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="141" t="s">
+      <c r="A46" s="583" t="s">
         <v>20</v>
       </c>
-      <c r="B46" s="142" t="s">
+      <c r="B46" s="584" t="s">
         <v>31</v>
       </c>
-      <c r="C46" s="143">
+      <c r="C46" s="585">
         <v>-0.19339332160707762</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="144" t="s">
+      <c r="A47" s="586" t="s">
         <v>20</v>
       </c>
-      <c r="B47" s="145" t="s">
+      <c r="B47" s="587" t="s">
         <v>32</v>
       </c>
-      <c r="C47" s="146">
+      <c r="C47" s="588">
         <v>0.082021414349730648</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="147" t="s">
+      <c r="A48" s="589" t="s">
         <v>20</v>
       </c>
-      <c r="B48" s="148" t="s">
+      <c r="B48" s="590" t="s">
         <v>33</v>
       </c>
-      <c r="C48" s="149">
+      <c r="C48" s="591">
         <v>0.16772307293749067</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="150" t="s">
+      <c r="A49" s="592" t="s">
         <v>20</v>
       </c>
-      <c r="B49" s="151" t="s">
+      <c r="B49" s="593" t="s">
         <v>34</v>
       </c>
-      <c r="C49" s="152">
+      <c r="C49" s="594">
         <v>0.28372599353407135</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="153" t="s">
+      <c r="A50" s="595" t="s">
         <v>20</v>
       </c>
-      <c r="B50" s="154" t="s">
+      <c r="B50" s="596" t="s">
         <v>35</v>
       </c>
-      <c r="C50" s="155">
+      <c r="C50" s="597">
         <v>0.35994881097310089</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="156" t="s">
+      <c r="A51" s="598" t="s">
         <v>20</v>
       </c>
-      <c r="B51" s="157" t="s">
+      <c r="B51" s="599" t="s">
         <v>36</v>
       </c>
-      <c r="C51" s="158">
+      <c r="C51" s="600">
         <v>0.55044347976266916</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="159" t="s">
+      <c r="A52" s="601" t="s">
         <v>20</v>
       </c>
-      <c r="B52" s="160" t="s">
+      <c r="B52" s="602" t="s">
         <v>37</v>
       </c>
-      <c r="C52" s="161">
+      <c r="C52" s="603">
         <v>0.17360999351281564</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="162" t="s">
+      <c r="A53" s="604" t="s">
         <v>20</v>
       </c>
-      <c r="B53" s="163" t="s">
+      <c r="B53" s="605" t="s">
         <v>38</v>
       </c>
-      <c r="C53" s="164">
+      <c r="C53" s="606">
         <v>-0.058382322166886796</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="165" t="s">
+      <c r="A54" s="607" t="s">
         <v>20</v>
       </c>
-      <c r="B54" s="166" t="s">
+      <c r="B54" s="608" t="s">
         <v>39</v>
       </c>
-      <c r="C54" s="167">
+      <c r="C54" s="609">
         <v>-0.0066104068289576309</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="168" t="s">
+      <c r="A55" s="610" t="s">
         <v>20</v>
       </c>
-      <c r="B55" s="169" t="s">
+      <c r="B55" s="611" t="s">
         <v>40</v>
       </c>
-      <c r="C55" s="170">
+      <c r="C55" s="612">
         <v>-0.37791365413044736</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="171" t="s">
+      <c r="A56" s="613" t="s">
         <v>20</v>
       </c>
-      <c r="B56" s="172" t="s">
+      <c r="B56" s="614" t="s">
         <v>41</v>
       </c>
-      <c r="C56" s="173">
+      <c r="C56" s="615">
         <v>-0.06887088384226478</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="174" t="s">
+      <c r="A57" s="616" t="s">
         <v>20</v>
       </c>
-      <c r="B57" s="175" t="s">
+      <c r="B57" s="617" t="s">
         <v>42</v>
       </c>
-      <c r="C57" s="176">
+      <c r="C57" s="618">
         <v>-0.0017457466573949252</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="177" t="s">
+      <c r="A58" s="619" t="s">
         <v>20</v>
       </c>
-      <c r="B58" s="178" t="s">
+      <c r="B58" s="620" t="s">
         <v>43</v>
       </c>
-      <c r="C58" s="179">
+      <c r="C58" s="621">
         <v>0.071455446588801805</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="180" t="s">
+      <c r="A59" s="622" t="s">
         <v>20</v>
       </c>
-      <c r="B59" s="181" t="s">
+      <c r="B59" s="623" t="s">
         <v>44</v>
       </c>
-      <c r="C59" s="182">
+      <c r="C59" s="624">
         <v>0.057619383296902693</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="183" t="s">
+      <c r="A60" s="625" t="s">
         <v>20</v>
       </c>
-      <c r="B60" s="184" t="s">
+      <c r="B60" s="626" t="s">
         <v>45</v>
       </c>
-      <c r="C60" s="185">
+      <c r="C60" s="627">
         <v>0.038556954402932053</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="186" t="s">
+      <c r="A61" s="628" t="s">
         <v>20</v>
       </c>
-      <c r="B61" s="187" t="s">
+      <c r="B61" s="629" t="s">
         <v>46</v>
       </c>
-      <c r="C61" s="188">
+      <c r="C61" s="630">
         <v>0.04728811525590354</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="189" t="s">
+      <c r="A62" s="631" t="s">
         <v>20</v>
       </c>
-      <c r="B62" s="190" t="s">
+      <c r="B62" s="632" t="s">
         <v>47</v>
       </c>
-      <c r="C62" s="191">
+      <c r="C62" s="633">
         <v>0.10922760256991892</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="192" t="s">
+      <c r="A63" s="634" t="s">
         <v>20</v>
       </c>
-      <c r="B63" s="193" t="s">
+      <c r="B63" s="635" t="s">
         <v>48</v>
       </c>
-      <c r="C63" s="194">
+      <c r="C63" s="636">
         <v>0.086324738373053406</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="195" t="s">
+      <c r="A64" s="637" t="s">
         <v>20</v>
       </c>
-      <c r="B64" s="196" t="s">
+      <c r="B64" s="638" t="s">
         <v>49</v>
       </c>
-      <c r="C64" s="197">
+      <c r="C64" s="639">
         <v>0.0672352196615838</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="198" t="s">
+      <c r="A65" s="640" t="s">
         <v>20</v>
       </c>
-      <c r="B65" s="199" t="s">
+      <c r="B65" s="641" t="s">
         <v>50</v>
       </c>
-      <c r="C65" s="200">
+      <c r="C65" s="642">
         <v>0.1189765203406974</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="201" t="s">
+      <c r="A66" s="643" t="s">
         <v>20</v>
       </c>
-      <c r="B66" s="202" t="s">
+      <c r="B66" s="644" t="s">
         <v>51</v>
       </c>
-      <c r="C66" s="203">
+      <c r="C66" s="645">
         <v>0.0011005227989281871</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="204" t="s">
+      <c r="A67" s="646" t="s">
         <v>20</v>
       </c>
-      <c r="B67" s="205" t="s">
+      <c r="B67" s="647" t="s">
         <v>52</v>
       </c>
-      <c r="C67" s="206">
+      <c r="C67" s="648">
         <v>-0.017534558437206797</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="207" t="s">
+      <c r="A68" s="649" t="s">
         <v>20</v>
       </c>
-      <c r="B68" s="208" t="s">
+      <c r="B68" s="650" t="s">
         <v>53</v>
       </c>
-      <c r="C68" s="209">
+      <c r="C68" s="651">
         <v>0.018201003901143101</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="210" t="s">
+      <c r="A69" s="652" t="s">
         <v>20</v>
       </c>
-      <c r="B69" s="211" t="s">
+      <c r="B69" s="653" t="s">
         <v>54</v>
       </c>
-      <c r="C69" s="212">
+      <c r="C69" s="654">
         <v>0.030646179110110257</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="213" t="s">
+      <c r="A70" s="655" t="s">
         <v>20</v>
       </c>
-      <c r="B70" s="214" t="s">
+      <c r="B70" s="656" t="s">
         <v>55</v>
       </c>
-      <c r="C70" s="215">
+      <c r="C70" s="657">
         <v>0.12495500016542459</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="216" t="s">
+      <c r="A71" s="658" t="s">
         <v>20</v>
       </c>
-      <c r="B71" s="217" t="s">
+      <c r="B71" s="659" t="s">
         <v>56</v>
       </c>
-      <c r="C71" s="218">
+      <c r="C71" s="660">
         <v>-0.0094373723332421416</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="219" t="s">
+      <c r="A72" s="661" t="s">
         <v>20</v>
       </c>
-      <c r="B72" s="220" t="s">
+      <c r="B72" s="662" t="s">
         <v>57</v>
       </c>
-      <c r="C72" s="221">
+      <c r="C72" s="663">
         <v>-0.00036661670728846407</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="222" t="s">
+      <c r="A73" s="664" t="s">
         <v>20</v>
       </c>
-      <c r="B73" s="223" t="s">
+      <c r="B73" s="665" t="s">
         <v>58</v>
       </c>
-      <c r="C73" s="224">
+      <c r="C73" s="666">
         <v>-6.8979216994948862</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="225" t="s">
+      <c r="A74" s="667" t="s">
         <v>21</v>
       </c>
-      <c r="B74" s="226" t="s">
+      <c r="B74" s="668" t="s">
         <v>23</v>
       </c>
-      <c r="C74" s="227">
+      <c r="C74" s="669">
         <v>-0.20895121092042776</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="228" t="s">
+      <c r="A75" s="670" t="s">
         <v>21</v>
       </c>
-      <c r="B75" s="229" t="s">
+      <c r="B75" s="671" t="s">
         <v>24</v>
       </c>
-      <c r="C75" s="230">
+      <c r="C75" s="672">
         <v>-0.23275173807332247</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="231" t="s">
+      <c r="A76" s="673" t="s">
         <v>21</v>
       </c>
-      <c r="B76" s="232" t="s">
+      <c r="B76" s="674" t="s">
         <v>25</v>
       </c>
-      <c r="C76" s="233">
+      <c r="C76" s="675">
         <v>-0.038733279082676382</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="234" t="s">
+      <c r="A77" s="676" t="s">
         <v>21</v>
       </c>
-      <c r="B77" s="235" t="s">
+      <c r="B77" s="677" t="s">
         <v>26</v>
       </c>
-      <c r="C77" s="236">
+      <c r="C77" s="678">
         <v>0.00029440788987272065</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="237" t="s">
+      <c r="A78" s="679" t="s">
         <v>21</v>
       </c>
-      <c r="B78" s="238" t="s">
+      <c r="B78" s="680" t="s">
         <v>27</v>
       </c>
-      <c r="C78" s="239">
+      <c r="C78" s="681">
         <v>0.14198736596211825</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="240" t="s">
+      <c r="A79" s="682" t="s">
         <v>21</v>
       </c>
-      <c r="B79" s="241" t="s">
+      <c r="B79" s="683" t="s">
         <v>28</v>
       </c>
-      <c r="C79" s="242">
+      <c r="C79" s="684">
         <v>0.07954032968913588</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="243" t="s">
+      <c r="A80" s="685" t="s">
         <v>21</v>
       </c>
-      <c r="B80" s="244" t="s">
+      <c r="B80" s="686" t="s">
         <v>29</v>
       </c>
-      <c r="C80" s="245">
+      <c r="C80" s="687">
         <v>-0.3006575772362694</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="246" t="s">
+      <c r="A81" s="688" t="s">
         <v>21</v>
       </c>
-      <c r="B81" s="247" t="s">
+      <c r="B81" s="689" t="s">
         <v>30</v>
       </c>
-      <c r="C81" s="248">
+      <c r="C81" s="690">
         <v>-0.38654786918660933</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="249" t="s">
+      <c r="A82" s="691" t="s">
         <v>21</v>
       </c>
-      <c r="B82" s="250" t="s">
+      <c r="B82" s="692" t="s">
         <v>31</v>
       </c>
-      <c r="C82" s="251">
+      <c r="C82" s="693">
         <v>-0.13292647027185817</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="252" t="s">
+      <c r="A83" s="694" t="s">
         <v>21</v>
       </c>
-      <c r="B83" s="253" t="s">
+      <c r="B83" s="695" t="s">
         <v>32</v>
       </c>
-      <c r="C83" s="254">
+      <c r="C83" s="696">
         <v>0.042730570926630226</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="255" t="s">
+      <c r="A84" s="697" t="s">
         <v>21</v>
       </c>
-      <c r="B84" s="256" t="s">
+      <c r="B84" s="698" t="s">
         <v>33</v>
       </c>
-      <c r="C84" s="257">
+      <c r="C84" s="699">
         <v>0.012217436746870862</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="258" t="s">
+      <c r="A85" s="700" t="s">
         <v>21</v>
       </c>
-      <c r="B85" s="259" t="s">
+      <c r="B85" s="701" t="s">
         <v>34</v>
       </c>
-      <c r="C85" s="260">
+      <c r="C85" s="702">
         <v>0.056297260346623544</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="261" t="s">
+      <c r="A86" s="703" t="s">
         <v>21</v>
       </c>
-      <c r="B86" s="262" t="s">
+      <c r="B86" s="704" t="s">
         <v>35</v>
       </c>
-      <c r="C86" s="263">
+      <c r="C86" s="705">
         <v>0.11927166541180617</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="264" t="s">
+      <c r="A87" s="706" t="s">
         <v>21</v>
       </c>
-      <c r="B87" s="265" t="s">
+      <c r="B87" s="707" t="s">
         <v>36</v>
       </c>
-      <c r="C87" s="266">
+      <c r="C87" s="708">
         <v>0.30645279876026094</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="267" t="s">
+      <c r="A88" s="709" t="s">
         <v>21</v>
       </c>
-      <c r="B88" s="268" t="s">
+      <c r="B88" s="710" t="s">
         <v>37</v>
       </c>
-      <c r="C88" s="269">
+      <c r="C88" s="711">
         <v>0.068174579139437724</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="270" t="s">
+      <c r="A89" s="712" t="s">
         <v>21</v>
       </c>
-      <c r="B89" s="271" t="s">
+      <c r="B89" s="713" t="s">
         <v>38</v>
       </c>
-      <c r="C89" s="272">
+      <c r="C89" s="714">
         <v>0.0090473036639792809</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="273" t="s">
+      <c r="A90" s="715" t="s">
         <v>21</v>
       </c>
-      <c r="B90" s="274" t="s">
+      <c r="B90" s="716" t="s">
         <v>39</v>
       </c>
-      <c r="C90" s="275">
+      <c r="C90" s="717">
         <v>-0.0066104068289573699</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="276" t="s">
+      <c r="A91" s="718" t="s">
         <v>21</v>
       </c>
-      <c r="B91" s="277" t="s">
+      <c r="B91" s="719" t="s">
         <v>40</v>
       </c>
-      <c r="C91" s="278">
+      <c r="C91" s="720">
         <v>-0.27169506286547818</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="279" t="s">
+      <c r="A92" s="721" t="s">
         <v>21</v>
       </c>
-      <c r="B92" s="280" t="s">
+      <c r="B92" s="722" t="s">
         <v>41</v>
       </c>
-      <c r="C92" s="281">
+      <c r="C92" s="723">
         <v>-0.06887088384226428</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="282" t="s">
+      <c r="A93" s="724" t="s">
         <v>21</v>
       </c>
-      <c r="B93" s="283" t="s">
+      <c r="B93" s="725" t="s">
         <v>42</v>
       </c>
-      <c r="C93" s="284">
+      <c r="C93" s="726">
         <v>-0.0017457466573954279</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="285" t="s">
+      <c r="A94" s="727" t="s">
         <v>21</v>
       </c>
-      <c r="B94" s="286" t="s">
+      <c r="B94" s="728" t="s">
         <v>43</v>
       </c>
-      <c r="C94" s="287">
+      <c r="C94" s="729">
         <v>0.024076641566481628</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="288" t="s">
+      <c r="A95" s="730" t="s">
         <v>21</v>
       </c>
-      <c r="B95" s="289" t="s">
+      <c r="B95" s="731" t="s">
         <v>44</v>
       </c>
-      <c r="C95" s="290">
+      <c r="C95" s="732">
         <v>0.032301748142646892</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="291" t="s">
+      <c r="A96" s="733" t="s">
         <v>21</v>
       </c>
-      <c r="B96" s="292" t="s">
+      <c r="B96" s="734" t="s">
         <v>45</v>
       </c>
-      <c r="C96" s="293">
+      <c r="C96" s="735">
         <v>0.057158068328157181</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="294" t="s">
+      <c r="A97" s="736" t="s">
         <v>21</v>
       </c>
-      <c r="B97" s="295" t="s">
+      <c r="B97" s="737" t="s">
         <v>46</v>
       </c>
-      <c r="C97" s="296">
+      <c r="C97" s="738">
         <v>-0.0066672692474687503</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="297" t="s">
+      <c r="A98" s="739" t="s">
         <v>21</v>
       </c>
-      <c r="B98" s="298" t="s">
+      <c r="B98" s="740" t="s">
         <v>47</v>
       </c>
-      <c r="C98" s="299">
+      <c r="C98" s="741">
         <v>0.031685511852720193</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="300" t="s">
+      <c r="A99" s="742" t="s">
         <v>21</v>
       </c>
-      <c r="B99" s="301" t="s">
+      <c r="B99" s="743" t="s">
         <v>48</v>
       </c>
-      <c r="C99" s="302">
+      <c r="C99" s="744">
         <v>0.088172187756468054</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="303" t="s">
+      <c r="A100" s="745" t="s">
         <v>21</v>
       </c>
-      <c r="B100" s="304" t="s">
+      <c r="B100" s="746" t="s">
         <v>49</v>
       </c>
-      <c r="C100" s="305">
+      <c r="C100" s="747">
         <v>0.067235219661581441</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="306" t="s">
+      <c r="A101" s="748" t="s">
         <v>21</v>
       </c>
-      <c r="B101" s="307" t="s">
+      <c r="B101" s="749" t="s">
         <v>50</v>
       </c>
-      <c r="C101" s="308">
+      <c r="C101" s="750">
         <v>0.11897652034069768</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="309" t="s">
+      <c r="A102" s="751" t="s">
         <v>21</v>
       </c>
-      <c r="B102" s="310" t="s">
+      <c r="B102" s="752" t="s">
         <v>51</v>
       </c>
-      <c r="C102" s="311">
+      <c r="C102" s="753">
         <v>0.12189393681901355</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="312" t="s">
+      <c r="A103" s="754" t="s">
         <v>21</v>
       </c>
-      <c r="B103" s="313" t="s">
+      <c r="B103" s="755" t="s">
         <v>52</v>
       </c>
-      <c r="C103" s="314">
+      <c r="C103" s="756">
         <v>-0.056553765717625694</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="315" t="s">
+      <c r="A104" s="757" t="s">
         <v>21</v>
       </c>
-      <c r="B104" s="316" t="s">
+      <c r="B104" s="758" t="s">
         <v>53</v>
       </c>
-      <c r="C104" s="317">
+      <c r="C104" s="759">
         <v>0.018201003901144312</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="318" t="s">
+      <c r="A105" s="760" t="s">
         <v>21</v>
       </c>
-      <c r="B105" s="319" t="s">
+      <c r="B105" s="761" t="s">
         <v>54</v>
       </c>
-      <c r="C105" s="320">
+      <c r="C105" s="762">
         <v>0.10264029595422537</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="321" t="s">
+      <c r="A106" s="763" t="s">
         <v>21</v>
       </c>
-      <c r="B106" s="322" t="s">
+      <c r="B106" s="764" t="s">
         <v>55</v>
       </c>
-      <c r="C106" s="323">
+      <c r="C106" s="765">
         <v>-0.16724062605833048</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="324" t="s">
+      <c r="A107" s="766" t="s">
         <v>21</v>
       </c>
-      <c r="B107" s="325" t="s">
+      <c r="B107" s="767" t="s">
         <v>56</v>
       </c>
-      <c r="C107" s="326">
+      <c r="C107" s="768">
         <v>-0.0094373723332439041</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="327" t="s">
+      <c r="A108" s="769" t="s">
         <v>21</v>
       </c>
-      <c r="B108" s="328" t="s">
+      <c r="B108" s="770" t="s">
         <v>57</v>
       </c>
-      <c r="C108" s="329">
+      <c r="C108" s="771">
         <v>-0.00036661670728811713</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="330" t="s">
+      <c r="A109" s="772" t="s">
         <v>21</v>
       </c>
-      <c r="B109" s="331" t="s">
+      <c r="B109" s="773" t="s">
         <v>58</v>
       </c>
-      <c r="C109" s="332">
+      <c r="C109" s="774">
         <v>-9.1705674926307292</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="333" t="s">
+      <c r="A110" s="775" t="s">
         <v>22</v>
       </c>
-      <c r="B110" s="334" t="s">
+      <c r="B110" s="776" t="s">
         <v>23</v>
       </c>
-      <c r="C110" s="335">
+      <c r="C110" s="777">
         <v>-0.080443559029333464</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="336" t="s">
+      <c r="A111" s="778" t="s">
         <v>22</v>
       </c>
-      <c r="B111" s="337" t="s">
+      <c r="B111" s="779" t="s">
         <v>24</v>
       </c>
-      <c r="C111" s="338">
+      <c r="C111" s="780">
         <v>-0.07053774812057334</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="339" t="s">
+      <c r="A112" s="781" t="s">
         <v>22</v>
       </c>
-      <c r="B112" s="340" t="s">
+      <c r="B112" s="782" t="s">
         <v>25</v>
       </c>
-      <c r="C112" s="341">
+      <c r="C112" s="783">
         <v>-0.036566506167624149</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="342" t="s">
+      <c r="A113" s="784" t="s">
         <v>22</v>
       </c>
-      <c r="B113" s="343" t="s">
+      <c r="B113" s="785" t="s">
         <v>26</v>
       </c>
-      <c r="C113" s="344">
+      <c r="C113" s="786">
         <v>0.00024591256256106808</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="345" t="s">
+      <c r="A114" s="787" t="s">
         <v>22</v>
       </c>
-      <c r="B114" s="346" t="s">
+      <c r="B114" s="788" t="s">
         <v>27</v>
       </c>
-      <c r="C114" s="347">
+      <c r="C114" s="789">
         <v>0.1639085212822414</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="348" t="s">
+      <c r="A115" s="790" t="s">
         <v>22</v>
       </c>
-      <c r="B115" s="349" t="s">
+      <c r="B115" s="791" t="s">
         <v>28</v>
       </c>
-      <c r="C115" s="350">
+      <c r="C115" s="792">
         <v>0.092498267325575673</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="351" t="s">
+      <c r="A116" s="793" t="s">
         <v>22</v>
       </c>
-      <c r="B116" s="352" t="s">
+      <c r="B116" s="794" t="s">
         <v>29</v>
       </c>
-      <c r="C116" s="353">
+      <c r="C116" s="795">
         <v>-0.29853383384047361</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="354" t="s">
+      <c r="A117" s="796" t="s">
         <v>22</v>
       </c>
-      <c r="B117" s="355" t="s">
+      <c r="B117" s="797" t="s">
         <v>30</v>
       </c>
-      <c r="C117" s="356">
+      <c r="C117" s="798">
         <v>-0.26020542634043486</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="357" t="s">
+      <c r="A118" s="799" t="s">
         <v>22</v>
       </c>
-      <c r="B118" s="358" t="s">
+      <c r="B118" s="800" t="s">
         <v>31</v>
       </c>
-      <c r="C118" s="359">
+      <c r="C118" s="801">
         <v>-0.0012254645782117449</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="360" t="s">
+      <c r="A119" s="802" t="s">
         <v>22</v>
       </c>
-      <c r="B119" s="361" t="s">
+      <c r="B119" s="803" t="s">
         <v>32</v>
       </c>
-      <c r="C119" s="362">
+      <c r="C119" s="804">
         <v>-0.11046360388771481</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="363" t="s">
+      <c r="A120" s="805" t="s">
         <v>22</v>
       </c>
-      <c r="B120" s="364" t="s">
+      <c r="B120" s="806" t="s">
         <v>33</v>
       </c>
-      <c r="C120" s="365">
+      <c r="C120" s="807">
         <v>-0.079761165472782322</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="366" t="s">
+      <c r="A121" s="808" t="s">
         <v>22</v>
       </c>
-      <c r="B121" s="367" t="s">
+      <c r="B121" s="809" t="s">
         <v>34</v>
       </c>
-      <c r="C121" s="368">
+      <c r="C121" s="810">
         <v>-0.055400099464370356</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="369" t="s">
+      <c r="A122" s="811" t="s">
         <v>22</v>
       </c>
-      <c r="B122" s="370" t="s">
+      <c r="B122" s="812" t="s">
         <v>35</v>
       </c>
-      <c r="C122" s="371">
+      <c r="C122" s="813">
         <v>-0.062113530588093234</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="372" t="s">
+      <c r="A123" s="814" t="s">
         <v>22</v>
       </c>
-      <c r="B123" s="373" t="s">
+      <c r="B123" s="815" t="s">
         <v>36</v>
       </c>
-      <c r="C123" s="374">
+      <c r="C123" s="816">
         <v>0.13777771389636911</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="375" t="s">
+      <c r="A124" s="817" t="s">
         <v>22</v>
       </c>
-      <c r="B124" s="376" t="s">
+      <c r="B124" s="818" t="s">
         <v>37</v>
       </c>
-      <c r="C124" s="377">
+      <c r="C124" s="819">
         <v>0.072521056019990635</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="378" t="s">
+      <c r="A125" s="820" t="s">
         <v>22</v>
       </c>
-      <c r="B125" s="379" t="s">
+      <c r="B125" s="821" t="s">
         <v>38</v>
       </c>
-      <c r="C125" s="380">
+      <c r="C125" s="822">
         <v>0.1192032019886516</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="381" t="s">
+      <c r="A126" s="823" t="s">
         <v>22</v>
       </c>
-      <c r="B126" s="382" t="s">
+      <c r="B126" s="824" t="s">
         <v>39</v>
       </c>
-      <c r="C126" s="383">
+      <c r="C126" s="825">
         <v>-0.0066104068289574176</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="384" t="s">
+      <c r="A127" s="826" t="s">
         <v>22</v>
       </c>
-      <c r="B127" s="385" t="s">
+      <c r="B127" s="827" t="s">
         <v>40</v>
       </c>
-      <c r="C127" s="386">
+      <c r="C127" s="828">
         <v>-0.023927175481323171</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="387" t="s">
+      <c r="A128" s="829" t="s">
         <v>22</v>
       </c>
-      <c r="B128" s="388" t="s">
+      <c r="B128" s="830" t="s">
         <v>41</v>
       </c>
-      <c r="C128" s="389">
+      <c r="C128" s="831">
         <v>-0.068870883842264655</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="390" t="s">
+      <c r="A129" s="832" t="s">
         <v>22</v>
       </c>
-      <c r="B129" s="391" t="s">
+      <c r="B129" s="833" t="s">
         <v>42</v>
       </c>
-      <c r="C129" s="392">
+      <c r="C129" s="834">
         <v>-0.0017457466573962553</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="393" t="s">
+      <c r="A130" s="835" t="s">
         <v>22</v>
       </c>
-      <c r="B130" s="394" t="s">
+      <c r="B130" s="836" t="s">
         <v>43</v>
       </c>
-      <c r="C130" s="395">
+      <c r="C130" s="837">
         <v>-0.13632084967825966</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="396" t="s">
+      <c r="A131" s="838" t="s">
         <v>22</v>
       </c>
-      <c r="B131" s="397" t="s">
+      <c r="B131" s="839" t="s">
         <v>44</v>
       </c>
-      <c r="C131" s="398">
+      <c r="C131" s="840">
         <v>-0.053107416113070897</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="399" t="s">
+      <c r="A132" s="841" t="s">
         <v>22</v>
       </c>
-      <c r="B132" s="400" t="s">
+      <c r="B132" s="842" t="s">
         <v>45</v>
       </c>
-      <c r="C132" s="401">
+      <c r="C132" s="843">
         <v>-0.034694044180575201</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="402" t="s">
+      <c r="A133" s="844" t="s">
         <v>22</v>
       </c>
-      <c r="B133" s="403" t="s">
+      <c r="B133" s="845" t="s">
         <v>46</v>
       </c>
-      <c r="C133" s="404">
+      <c r="C133" s="846">
         <v>-0.1207169521782252</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="405" t="s">
+      <c r="A134" s="847" t="s">
         <v>22</v>
       </c>
-      <c r="B134" s="406" t="s">
+      <c r="B134" s="848" t="s">
         <v>47</v>
       </c>
-      <c r="C134" s="407">
+      <c r="C134" s="849">
         <v>-0.037614203839197106</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="408" t="s">
+      <c r="A135" s="850" t="s">
         <v>22</v>
       </c>
-      <c r="B135" s="409" t="s">
+      <c r="B135" s="851" t="s">
         <v>48</v>
       </c>
-      <c r="C135" s="410">
+      <c r="C135" s="852">
         <v>-0.059741847912303636</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="411" t="s">
+      <c r="A136" s="853" t="s">
         <v>22</v>
       </c>
-      <c r="B136" s="412" t="s">
+      <c r="B136" s="854" t="s">
         <v>49</v>
       </c>
-      <c r="C136" s="413">
+      <c r="C136" s="855">
         <v>0.067235219661582676</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="414" t="s">
+      <c r="A137" s="856" t="s">
         <v>22</v>
       </c>
-      <c r="B137" s="415" t="s">
+      <c r="B137" s="857" t="s">
         <v>50</v>
       </c>
-      <c r="C137" s="416">
+      <c r="C137" s="858">
         <v>0.11897652034069733</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="417" t="s">
+      <c r="A138" s="859" t="s">
         <v>22</v>
       </c>
-      <c r="B138" s="418" t="s">
+      <c r="B138" s="860" t="s">
         <v>51</v>
       </c>
-      <c r="C138" s="419">
+      <c r="C138" s="861">
         <v>-0.035403770060102369</v>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="420" t="s">
+      <c r="A139" s="862" t="s">
         <v>22</v>
       </c>
-      <c r="B139" s="421" t="s">
+      <c r="B139" s="863" t="s">
         <v>52</v>
       </c>
-      <c r="C139" s="422">
+      <c r="C139" s="864">
         <v>-0.083570455027712889</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="423" t="s">
+      <c r="A140" s="865" t="s">
         <v>22</v>
       </c>
-      <c r="B140" s="424" t="s">
+      <c r="B140" s="866" t="s">
         <v>53</v>
       </c>
-      <c r="C140" s="425">
+      <c r="C140" s="867">
         <v>0.018201003901142477</v>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="426" t="s">
+      <c r="A141" s="868" t="s">
         <v>22</v>
       </c>
-      <c r="B141" s="427" t="s">
+      <c r="B141" s="869" t="s">
         <v>54</v>
       </c>
-      <c r="C141" s="428">
+      <c r="C141" s="870">
         <v>0.0060034191143518659</v>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="429" t="s">
+      <c r="A142" s="871" t="s">
         <v>22</v>
       </c>
-      <c r="B142" s="430" t="s">
+      <c r="B142" s="872" t="s">
         <v>55</v>
       </c>
-      <c r="C142" s="431">
+      <c r="C142" s="873">
         <v>0.0031718414010284569</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="432" t="s">
+      <c r="A143" s="874" t="s">
         <v>22</v>
       </c>
-      <c r="B143" s="433" t="s">
+      <c r="B143" s="875" t="s">
         <v>56</v>
       </c>
-      <c r="C143" s="434">
+      <c r="C143" s="876">
         <v>-0.0094373723332433213</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="435" t="s">
+      <c r="A144" s="877" t="s">
         <v>22</v>
       </c>
-      <c r="B144" s="436" t="s">
+      <c r="B144" s="878" t="s">
         <v>57</v>
       </c>
-      <c r="C144" s="437">
+      <c r="C144" s="879">
         <v>-0.00036661670728767304</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="438" t="s">
+      <c r="A145" s="880" t="s">
         <v>22</v>
       </c>
-      <c r="B145" s="439" t="s">
+      <c r="B145" s="881" t="s">
         <v>58</v>
       </c>
-      <c r="C145" s="440">
+      <c r="C145" s="882">
         <v>-12.783531940490784</v>
       </c>
     </row>
